--- a/InputData/elec/DRC/cn-Demand Response Capacity.xlsx
+++ b/InputData/elec/DRC/cn-Demand Response Capacity.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12400" activeTab="4"/>
+    <workbookView windowWidth="27952" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -366,19 +366,19 @@
     <t>Policy Setting</t>
   </si>
   <si>
-    <t>Total Capacity Limit（%）</t>
-  </si>
-  <si>
-    <t>Current Capacity Limit (万千瓦）</t>
-  </si>
-  <si>
-    <t>Potential Capacity Limit (%)</t>
-  </si>
-  <si>
-    <t>% Potential Capacity Limit Achieved</t>
-  </si>
-  <si>
-    <t>Max Potential Capacity Limit Achieved</t>
+    <t>十五五情景（%）</t>
+  </si>
+  <si>
+    <t>十五五情景（value）</t>
+  </si>
+  <si>
+    <t>Potential Additional Value</t>
+  </si>
+  <si>
+    <t>Potential Additional %</t>
+  </si>
+  <si>
+    <t>Max Value</t>
   </si>
   <si>
     <t>DR Capacity (MW)</t>
@@ -391,14 +391,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0%"/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -614,13 +613,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1052,7 +1051,7 @@
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1098,7 +1097,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1109,21 +1108,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1243,8 +1238,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7674610" y="177800"/>
-          <a:ext cx="5248910" cy="1863725"/>
+          <a:off x="7884160" y="171450"/>
+          <a:ext cx="5386070" cy="1800225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1544,17 +1539,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1567,78 +1562,78 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:2">
+    <row r="7" spans="1:2">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:2">
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
+    <row r="9" spans="1:2">
       <c r="B9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="2:2">
+    <row r="10" spans="1:2">
       <c r="B10">
         <v>2023</v>
       </c>
     </row>
-    <row r="11" spans="2:2">
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="23" t="s">
+    <row r="12" spans="1:2">
+      <c r="B12" s="19" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="23"/>
-    </row>
-    <row r="14" spans="2:2">
+    <row r="13" spans="1:2">
+      <c r="B13" s="19"/>
+    </row>
+    <row r="14" spans="1:2">
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="24" t="s">
+    <row r="15" ht="13.9" spans="1:2">
+      <c r="B15" s="20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:2">
-      <c r="B16" s="25" t="s">
+    <row r="16" ht="13.9" spans="1:2">
+      <c r="B16" s="21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" ht="28" spans="2:2">
-      <c r="B17" s="24" t="s">
+    <row r="17" ht="27.75" spans="1:3">
+      <c r="B17" s="20" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="25" t="s">
+    <row r="18" ht="13.9" spans="1:3">
+      <c r="B18" s="21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="25" t="s">
+    <row r="19" ht="13.9" spans="1:3">
+      <c r="B19" s="21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="25"/>
-    </row>
-    <row r="21" spans="2:3">
+    <row r="20" ht="13.85" spans="1:3">
+      <c r="B20" s="21"/>
+    </row>
+    <row r="21" spans="1:3">
       <c r="B21" t="s">
         <v>16</v>
       </c>
@@ -1646,40 +1641,40 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1688,7 +1683,7 @@
       <c r="B34" s="1"/>
     </row>
     <row r="35" spans="2:2">
-      <c r="B35" s="26"/>
+      <c r="B35" s="22"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1704,497 +1699,497 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9" style="17"/>
-    <col min="2" max="2" width="16.1090909090909" style="17" customWidth="1"/>
-    <col min="4" max="4" width="15.1090909090909" customWidth="1"/>
-    <col min="5" max="7" width="17.2181818181818" customWidth="1"/>
+    <col min="1" max="1" width="9" style="13"/>
+    <col min="2" max="2" width="16.1061946902655" style="13" customWidth="1"/>
+    <col min="4" max="4" width="15.1061946902655" customWidth="1"/>
+    <col min="5" max="7" width="17.2212389380531" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="19" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="15">
         <v>2020</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="15">
         <f>MAX(E12:G12)</f>
         <v>700</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="15">
         <v>700</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="15">
         <v>300</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="15">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="15">
         <v>2021</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="15">
         <v>200</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19">
+      <c r="C17" s="15"/>
+      <c r="D17" s="15">
         <v>60</v>
       </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="15">
         <v>2020</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="15">
         <v>432</v>
       </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19">
+      <c r="C19" s="15"/>
+      <c r="D19" s="15">
         <v>117</v>
       </c>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19">
+      <c r="C20" s="15"/>
+      <c r="D20" s="15">
         <v>180</v>
       </c>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19">
+      <c r="C21" s="15"/>
+      <c r="D21" s="15">
         <v>19.8</v>
       </c>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="15">
         <v>2020</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="15">
         <v>40</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19">
+      <c r="C34" s="15"/>
+      <c r="D34" s="15">
         <f>SUM(D3:D33)</f>
         <v>1748.8</v>
       </c>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2212,27 +2207,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AP41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:AP42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="9.44545454545455" customWidth="1"/>
-    <col min="3" max="3" width="12.8181818181818"/>
+    <col min="2" max="2" width="9.44247787610619" customWidth="1"/>
+    <col min="3" max="3" width="12.8141592920354"/>
     <col min="4" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="12.8181818181818"/>
-    <col min="7" max="7" width="9.44545454545455" customWidth="1"/>
-    <col min="8" max="8" width="12.8181818181818"/>
-    <col min="9" max="9" width="9.44545454545455" customWidth="1"/>
-    <col min="10" max="12" width="12.8181818181818"/>
+    <col min="6" max="6" width="12.8141592920354"/>
+    <col min="7" max="7" width="9.44247787610619" customWidth="1"/>
+    <col min="8" max="8" width="12.8141592920354"/>
+    <col min="9" max="9" width="9.44247787610619" customWidth="1"/>
+    <col min="10" max="12" width="12.8141592920354"/>
     <col min="13" max="41" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:1">
+    <row r="1" s="4" customFormat="1" spans="1:42">
       <c r="A1" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="2:42">
+    <row r="2" spans="1:42">
       <c r="B2">
         <v>2020</v>
       </c>
@@ -2402,119 +2397,119 @@
         <f>18.9*100000000/10000</f>
         <v>189000</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="6">
         <f>$L$3+($AP$3-$L$3)*(M2-$L$2)/($AP$2-$L$2)</f>
         <v>192033.333333333</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="6">
         <f t="shared" ref="N3:AO3" si="1">$L$3+($AP$3-$L$3)*(N2-$L$2)/($AP$2-$L$2)</f>
         <v>195066.666666667</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="6">
         <f t="shared" si="1"/>
         <v>198100</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="6">
         <f t="shared" si="1"/>
         <v>201133.333333333</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="6">
         <f t="shared" si="1"/>
         <v>204166.666666667</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="6">
         <f t="shared" si="1"/>
         <v>207200</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="6">
         <f t="shared" si="1"/>
         <v>210233.333333333</v>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="6">
         <f t="shared" si="1"/>
         <v>213266.666666667</v>
       </c>
-      <c r="U3" s="14">
+      <c r="U3" s="6">
         <f t="shared" si="1"/>
         <v>216300</v>
       </c>
-      <c r="V3" s="14">
+      <c r="V3" s="6">
         <f t="shared" si="1"/>
         <v>219333.333333333</v>
       </c>
-      <c r="W3" s="14">
+      <c r="W3" s="6">
         <f t="shared" si="1"/>
         <v>222366.666666667</v>
       </c>
-      <c r="X3" s="14">
+      <c r="X3" s="6">
         <f t="shared" si="1"/>
         <v>225400</v>
       </c>
-      <c r="Y3" s="14">
+      <c r="Y3" s="6">
         <f t="shared" si="1"/>
         <v>228433.333333333</v>
       </c>
-      <c r="Z3" s="14">
+      <c r="Z3" s="6">
         <f t="shared" si="1"/>
         <v>231466.666666667</v>
       </c>
-      <c r="AA3" s="14">
+      <c r="AA3" s="6">
         <f t="shared" si="1"/>
         <v>234500</v>
       </c>
-      <c r="AB3" s="14">
+      <c r="AB3" s="6">
         <f t="shared" si="1"/>
         <v>237533.333333333</v>
       </c>
-      <c r="AC3" s="14">
+      <c r="AC3" s="6">
         <f t="shared" si="1"/>
         <v>240566.666666667</v>
       </c>
-      <c r="AD3" s="14">
+      <c r="AD3" s="6">
         <f t="shared" si="1"/>
         <v>243600</v>
       </c>
-      <c r="AE3" s="14">
+      <c r="AE3" s="6">
         <f t="shared" si="1"/>
         <v>246633.333333333</v>
       </c>
-      <c r="AF3" s="14">
+      <c r="AF3" s="6">
         <f t="shared" si="1"/>
         <v>249666.666666667</v>
       </c>
-      <c r="AG3" s="14">
+      <c r="AG3" s="6">
         <f t="shared" si="1"/>
         <v>252700</v>
       </c>
-      <c r="AH3" s="14">
+      <c r="AH3" s="6">
         <f t="shared" si="1"/>
         <v>255733.333333333</v>
       </c>
-      <c r="AI3" s="14">
+      <c r="AI3" s="6">
         <f t="shared" si="1"/>
         <v>258766.666666667</v>
       </c>
-      <c r="AJ3" s="14">
+      <c r="AJ3" s="6">
         <f t="shared" si="1"/>
         <v>261800</v>
       </c>
-      <c r="AK3" s="14">
+      <c r="AK3" s="6">
         <f t="shared" si="1"/>
         <v>264833.333333333</v>
       </c>
-      <c r="AL3" s="14">
+      <c r="AL3" s="6">
         <f t="shared" si="1"/>
         <v>267866.666666667</v>
       </c>
-      <c r="AM3" s="14">
+      <c r="AM3" s="6">
         <f t="shared" si="1"/>
         <v>270900</v>
       </c>
-      <c r="AN3" s="14">
+      <c r="AN3" s="6">
         <f t="shared" si="1"/>
         <v>273933.333333333</v>
       </c>
-      <c r="AO3" s="14">
+      <c r="AO3" s="6">
         <f t="shared" si="1"/>
         <v>276966.666666667</v>
       </c>
@@ -2692,7 +2687,7 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:42">
       <c r="A6" t="s">
         <v>100</v>
       </c>
@@ -2701,127 +2696,127 @@
       <c r="A7" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>0</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>0.006</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>0.012</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>0.018</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>0.024</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <v>0.03</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="8">
         <v>0.03</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="8">
         <v>0.03</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="8">
         <v>0.03</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="8">
         <v>0.03</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="8">
         <v>0.03</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="8">
         <v>0.03</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="8">
         <v>0.03</v>
       </c>
-      <c r="O7" s="7">
+      <c r="O7" s="8">
         <v>0.03</v>
       </c>
-      <c r="P7" s="7">
+      <c r="P7" s="8">
         <v>0.03</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="Q7" s="8">
         <v>0.03</v>
       </c>
-      <c r="R7" s="7">
+      <c r="R7" s="8">
         <v>0.03</v>
       </c>
-      <c r="S7" s="7">
+      <c r="S7" s="8">
         <v>0.03</v>
       </c>
-      <c r="T7" s="7">
+      <c r="T7" s="8">
         <v>0.03</v>
       </c>
-      <c r="U7" s="7">
+      <c r="U7" s="8">
         <v>0.03</v>
       </c>
-      <c r="V7" s="7">
+      <c r="V7" s="8">
         <v>0.03</v>
       </c>
-      <c r="W7" s="7">
+      <c r="W7" s="8">
         <v>0.03</v>
       </c>
-      <c r="X7" s="7">
+      <c r="X7" s="8">
         <v>0.03</v>
       </c>
-      <c r="Y7" s="7">
+      <c r="Y7" s="8">
         <v>0.03</v>
       </c>
-      <c r="Z7" s="7">
+      <c r="Z7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AA7" s="7">
+      <c r="AA7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AB7" s="7">
+      <c r="AB7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AC7" s="7">
+      <c r="AC7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AD7" s="7">
+      <c r="AD7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AE7" s="7">
+      <c r="AE7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AF7" s="7">
+      <c r="AF7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AG7" s="7">
+      <c r="AG7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AH7" s="7">
+      <c r="AH7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AI7" s="7">
+      <c r="AI7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AJ7" s="7">
+      <c r="AJ7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AK7" s="7">
+      <c r="AK7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AL7" s="7">
+      <c r="AL7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AM7" s="7">
+      <c r="AM7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AN7" s="7">
+      <c r="AN7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AO7" s="7">
+      <c r="AO7" s="8">
         <v>0.03</v>
       </c>
-      <c r="AP7" s="7">
+      <c r="AP7" s="8">
         <v>0.03</v>
       </c>
     </row>
@@ -2829,167 +2824,167 @@
       <c r="A8" t="s">
         <v>102</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="8">
         <f t="shared" ref="B8:AP8" si="3">B15</f>
         <v>0.04</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f t="shared" si="3"/>
         <v>0.046</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f t="shared" si="3"/>
         <v>0.052</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f t="shared" si="3"/>
         <v>0.058</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f t="shared" si="3"/>
         <v>0.064</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <f t="shared" si="3"/>
         <v>0.07</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="8">
         <f t="shared" si="3"/>
         <v>0.076</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="8">
         <f t="shared" si="3"/>
         <v>0.082</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="8">
         <f t="shared" si="3"/>
         <v>0.088</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="8">
         <f t="shared" si="3"/>
         <v>0.094</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="8">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="8">
         <f t="shared" si="3"/>
         <v>0.105</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="8">
         <f t="shared" si="3"/>
         <v>0.11</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="8">
         <f t="shared" si="3"/>
         <v>0.115</v>
       </c>
-      <c r="P8" s="7">
+      <c r="P8" s="8">
         <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="Q8" s="8">
         <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
-      <c r="R8" s="7">
+      <c r="R8" s="8">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
-      <c r="S8" s="7">
+      <c r="S8" s="8">
         <f t="shared" si="3"/>
         <v>0.135</v>
       </c>
-      <c r="T8" s="7">
+      <c r="T8" s="8">
         <f t="shared" si="3"/>
         <v>0.14</v>
       </c>
-      <c r="U8" s="7">
+      <c r="U8" s="8">
         <f t="shared" si="3"/>
         <v>0.145</v>
       </c>
-      <c r="V8" s="7">
+      <c r="V8" s="8">
         <f t="shared" si="3"/>
         <v>0.15</v>
       </c>
-      <c r="W8" s="7">
+      <c r="W8" s="8">
         <f t="shared" si="3"/>
         <v>0.155</v>
       </c>
-      <c r="X8" s="7">
+      <c r="X8" s="8">
         <f t="shared" si="3"/>
         <v>0.16</v>
       </c>
-      <c r="Y8" s="7">
+      <c r="Y8" s="8">
         <f t="shared" si="3"/>
         <v>0.165</v>
       </c>
-      <c r="Z8" s="7">
+      <c r="Z8" s="8">
         <f t="shared" si="3"/>
         <v>0.17</v>
       </c>
-      <c r="AA8" s="7">
+      <c r="AA8" s="8">
         <f t="shared" si="3"/>
         <v>0.175</v>
       </c>
-      <c r="AB8" s="7">
+      <c r="AB8" s="8">
         <f t="shared" si="3"/>
         <v>0.18</v>
       </c>
-      <c r="AC8" s="7">
+      <c r="AC8" s="8">
         <f t="shared" si="3"/>
         <v>0.185</v>
       </c>
-      <c r="AD8" s="7">
+      <c r="AD8" s="8">
         <f t="shared" si="3"/>
         <v>0.19</v>
       </c>
-      <c r="AE8" s="7">
+      <c r="AE8" s="8">
         <f t="shared" si="3"/>
         <v>0.195</v>
       </c>
-      <c r="AF8" s="7">
+      <c r="AF8" s="8">
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="AG8" s="7">
+      <c r="AG8" s="8">
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="AH8" s="7">
+      <c r="AH8" s="8">
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="AI8" s="7">
+      <c r="AI8" s="8">
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="AJ8" s="7">
+      <c r="AJ8" s="8">
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="AK8" s="7">
+      <c r="AK8" s="8">
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="AL8" s="7">
+      <c r="AL8" s="8">
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="AM8" s="7">
+      <c r="AM8" s="8">
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="AN8" s="7">
+      <c r="AN8" s="8">
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="AO8" s="7">
+      <c r="AO8" s="8">
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
-      <c r="AP8" s="7">
+      <c r="AP8" s="8">
         <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
@@ -2998,176 +2993,176 @@
       <c r="A9" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="8">
         <f>B8-B7</f>
         <v>0.04</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <f t="shared" ref="B9:F9" si="4">C8-C7</f>
         <v>0.04</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f t="shared" si="4"/>
         <v>0.04</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f t="shared" si="4"/>
         <v>0.04</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <f t="shared" si="4"/>
         <v>0.04</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <f t="shared" ref="G9:AO9" si="5">G8-G7</f>
         <v>0.04</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="8">
         <f t="shared" si="5"/>
         <v>0.046</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="8">
         <f t="shared" si="5"/>
         <v>0.052</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="8">
         <f t="shared" si="5"/>
         <v>0.058</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="8">
         <f t="shared" si="5"/>
         <v>0.064</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="8">
         <f t="shared" si="5"/>
         <v>0.07</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="8">
         <f t="shared" si="5"/>
         <v>0.075</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9" s="8">
         <f t="shared" si="5"/>
         <v>0.08</v>
       </c>
-      <c r="O9" s="7">
+      <c r="O9" s="8">
         <f t="shared" si="5"/>
         <v>0.085</v>
       </c>
-      <c r="P9" s="7">
+      <c r="P9" s="8">
         <f t="shared" si="5"/>
         <v>0.09</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="Q9" s="8">
         <f t="shared" si="5"/>
         <v>0.095</v>
       </c>
-      <c r="R9" s="7">
+      <c r="R9" s="8">
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="S9" s="7">
+      <c r="S9" s="8">
         <f t="shared" si="5"/>
         <v>0.105</v>
       </c>
-      <c r="T9" s="7">
+      <c r="T9" s="8">
         <f t="shared" si="5"/>
         <v>0.11</v>
       </c>
-      <c r="U9" s="7">
+      <c r="U9" s="8">
         <f t="shared" si="5"/>
         <v>0.115</v>
       </c>
-      <c r="V9" s="7">
+      <c r="V9" s="8">
         <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
-      <c r="W9" s="7">
+      <c r="W9" s="8">
         <f t="shared" si="5"/>
         <v>0.125</v>
       </c>
-      <c r="X9" s="7">
+      <c r="X9" s="8">
         <f t="shared" si="5"/>
         <v>0.13</v>
       </c>
-      <c r="Y9" s="7">
+      <c r="Y9" s="8">
         <f t="shared" si="5"/>
         <v>0.135</v>
       </c>
-      <c r="Z9" s="7">
+      <c r="Z9" s="8">
         <f t="shared" si="5"/>
         <v>0.14</v>
       </c>
-      <c r="AA9" s="7">
+      <c r="AA9" s="8">
         <f t="shared" si="5"/>
         <v>0.145</v>
       </c>
-      <c r="AB9" s="7">
+      <c r="AB9" s="8">
         <f t="shared" si="5"/>
         <v>0.15</v>
       </c>
-      <c r="AC9" s="7">
+      <c r="AC9" s="8">
         <f t="shared" si="5"/>
         <v>0.155</v>
       </c>
-      <c r="AD9" s="7">
+      <c r="AD9" s="8">
         <f t="shared" si="5"/>
         <v>0.16</v>
       </c>
-      <c r="AE9" s="7">
+      <c r="AE9" s="8">
         <f t="shared" si="5"/>
         <v>0.165</v>
       </c>
-      <c r="AF9" s="7">
+      <c r="AF9" s="8">
         <f t="shared" si="5"/>
         <v>0.17</v>
       </c>
-      <c r="AG9" s="7">
+      <c r="AG9" s="8">
         <f t="shared" si="5"/>
         <v>0.17</v>
       </c>
-      <c r="AH9" s="7">
+      <c r="AH9" s="8">
         <f t="shared" si="5"/>
         <v>0.17</v>
       </c>
-      <c r="AI9" s="7">
+      <c r="AI9" s="8">
         <f t="shared" si="5"/>
         <v>0.17</v>
       </c>
-      <c r="AJ9" s="7">
+      <c r="AJ9" s="8">
         <f t="shared" si="5"/>
         <v>0.17</v>
       </c>
-      <c r="AK9" s="7">
+      <c r="AK9" s="8">
         <f t="shared" si="5"/>
         <v>0.17</v>
       </c>
-      <c r="AL9" s="7">
+      <c r="AL9" s="8">
         <f t="shared" si="5"/>
         <v>0.17</v>
       </c>
-      <c r="AM9" s="7">
+      <c r="AM9" s="8">
         <f t="shared" si="5"/>
         <v>0.17</v>
       </c>
-      <c r="AN9" s="7">
+      <c r="AN9" s="8">
         <f t="shared" si="5"/>
         <v>0.17</v>
       </c>
-      <c r="AO9" s="7">
+      <c r="AO9" s="8">
         <f t="shared" si="5"/>
         <v>0.17</v>
       </c>
-      <c r="AP9" s="7">
+      <c r="AP9" s="8">
         <f t="shared" ref="AP9" si="6">AP8-AP7</f>
         <v>0.17</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:42">
       <c r="A11" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <v>1.5</v>
       </c>
     </row>
@@ -3176,155 +3171,155 @@
       <c r="A15" t="s">
         <v>105</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="9">
         <v>0.04</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="10">
         <f>$B$15+($L$15-$B$15)*(C2-$B$2)/($L$2-$B$2)</f>
         <v>0.046</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="10">
         <f t="shared" ref="D15:K15" si="7">$B$15+($L$15-$B$15)*(D2-$B$2)/($L$2-$B$2)</f>
         <v>0.052</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="10">
         <f t="shared" si="7"/>
         <v>0.058</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="10">
         <f t="shared" si="7"/>
         <v>0.064</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="10">
         <f t="shared" si="7"/>
         <v>0.07</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="10">
         <f t="shared" si="7"/>
         <v>0.076</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="10">
         <f t="shared" si="7"/>
         <v>0.082</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="10">
         <f t="shared" si="7"/>
         <v>0.088</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="10">
         <f t="shared" si="7"/>
         <v>0.094</v>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="11">
         <v>0.1</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="10">
         <f>$L$15+($AF$15-$L$15)*(M2-$L$2)/($AF$2-$L$2)</f>
         <v>0.105</v>
       </c>
-      <c r="N15" s="9">
+      <c r="N15" s="10">
         <f t="shared" ref="N15:AE15" si="8">$L$15+($AF$15-$L$15)*(N2-$L$2)/($AF$2-$L$2)</f>
         <v>0.11</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="10">
         <f t="shared" si="8"/>
         <v>0.115</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="10">
         <f t="shared" si="8"/>
         <v>0.12</v>
       </c>
-      <c r="Q15" s="9">
+      <c r="Q15" s="10">
         <f t="shared" si="8"/>
         <v>0.125</v>
       </c>
-      <c r="R15" s="9">
+      <c r="R15" s="10">
         <f t="shared" si="8"/>
         <v>0.13</v>
       </c>
-      <c r="S15" s="9">
+      <c r="S15" s="10">
         <f t="shared" si="8"/>
         <v>0.135</v>
       </c>
-      <c r="T15" s="9">
+      <c r="T15" s="10">
         <f t="shared" si="8"/>
         <v>0.14</v>
       </c>
-      <c r="U15" s="9">
+      <c r="U15" s="10">
         <f t="shared" si="8"/>
         <v>0.145</v>
       </c>
-      <c r="V15" s="9">
+      <c r="V15" s="10">
         <f t="shared" si="8"/>
         <v>0.15</v>
       </c>
-      <c r="W15" s="9">
+      <c r="W15" s="10">
         <f t="shared" si="8"/>
         <v>0.155</v>
       </c>
-      <c r="X15" s="9">
+      <c r="X15" s="10">
         <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
-      <c r="Y15" s="9">
+      <c r="Y15" s="10">
         <f t="shared" si="8"/>
         <v>0.165</v>
       </c>
-      <c r="Z15" s="9">
+      <c r="Z15" s="10">
         <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
-      <c r="AA15" s="9">
+      <c r="AA15" s="10">
         <f t="shared" si="8"/>
         <v>0.175</v>
       </c>
-      <c r="AB15" s="9">
+      <c r="AB15" s="10">
         <f t="shared" si="8"/>
         <v>0.18</v>
       </c>
-      <c r="AC15" s="9">
+      <c r="AC15" s="10">
         <f t="shared" si="8"/>
         <v>0.185</v>
       </c>
-      <c r="AD15" s="9">
+      <c r="AD15" s="10">
         <f t="shared" si="8"/>
         <v>0.19</v>
       </c>
-      <c r="AE15" s="9">
+      <c r="AE15" s="10">
         <f t="shared" si="8"/>
         <v>0.195</v>
       </c>
-      <c r="AF15" s="15">
+      <c r="AF15" s="11">
         <v>0.2</v>
       </c>
-      <c r="AG15" s="15">
+      <c r="AG15" s="11">
         <v>0.2</v>
       </c>
-      <c r="AH15" s="15">
+      <c r="AH15" s="11">
         <v>0.2</v>
       </c>
-      <c r="AI15" s="15">
+      <c r="AI15" s="11">
         <v>0.2</v>
       </c>
-      <c r="AJ15" s="15">
+      <c r="AJ15" s="11">
         <v>0.2</v>
       </c>
-      <c r="AK15" s="15">
+      <c r="AK15" s="11">
         <v>0.2</v>
       </c>
-      <c r="AL15" s="15">
+      <c r="AL15" s="11">
         <v>0.2</v>
       </c>
-      <c r="AM15" s="15">
+      <c r="AM15" s="11">
         <v>0.2</v>
       </c>
-      <c r="AN15" s="15">
+      <c r="AN15" s="11">
         <v>0.2</v>
       </c>
-      <c r="AO15" s="15">
+      <c r="AO15" s="11">
         <v>0.2</v>
       </c>
-      <c r="AP15" s="15">
+      <c r="AP15" s="11">
         <v>0.2</v>
       </c>
     </row>
@@ -3332,512 +3327,512 @@
       <c r="A16" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="10">
         <f>B15-B7</f>
         <v>0.04</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="10">
         <f t="shared" ref="C16:AP16" si="9">C15-C7</f>
         <v>0.04</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="10">
         <f t="shared" si="9"/>
         <v>0.04</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <f t="shared" si="9"/>
         <v>0.04</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="10">
         <f t="shared" si="9"/>
         <v>0.04</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="10">
         <f t="shared" si="9"/>
         <v>0.04</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="10">
         <f t="shared" si="9"/>
         <v>0.046</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="10">
         <f t="shared" si="9"/>
         <v>0.052</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="10">
         <f t="shared" si="9"/>
         <v>0.058</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="10">
         <f t="shared" si="9"/>
         <v>0.064</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="10">
         <f t="shared" si="9"/>
         <v>0.07</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="10">
         <f t="shared" si="9"/>
         <v>0.075</v>
       </c>
-      <c r="N16" s="9">
+      <c r="N16" s="10">
         <f t="shared" si="9"/>
         <v>0.08</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="10">
         <f t="shared" si="9"/>
         <v>0.085</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="10">
         <f t="shared" si="9"/>
         <v>0.09</v>
       </c>
-      <c r="Q16" s="9">
+      <c r="Q16" s="10">
         <f t="shared" si="9"/>
         <v>0.095</v>
       </c>
-      <c r="R16" s="9">
+      <c r="R16" s="10">
         <f t="shared" si="9"/>
         <v>0.1</v>
       </c>
-      <c r="S16" s="9">
+      <c r="S16" s="10">
         <f t="shared" si="9"/>
         <v>0.105</v>
       </c>
-      <c r="T16" s="9">
+      <c r="T16" s="10">
         <f t="shared" si="9"/>
         <v>0.11</v>
       </c>
-      <c r="U16" s="9">
+      <c r="U16" s="10">
         <f t="shared" si="9"/>
         <v>0.115</v>
       </c>
-      <c r="V16" s="9">
+      <c r="V16" s="10">
         <f t="shared" si="9"/>
         <v>0.12</v>
       </c>
-      <c r="W16" s="9">
+      <c r="W16" s="10">
         <f t="shared" si="9"/>
         <v>0.125</v>
       </c>
-      <c r="X16" s="9">
+      <c r="X16" s="10">
         <f t="shared" si="9"/>
         <v>0.13</v>
       </c>
-      <c r="Y16" s="9">
+      <c r="Y16" s="10">
         <f t="shared" si="9"/>
         <v>0.135</v>
       </c>
-      <c r="Z16" s="9">
+      <c r="Z16" s="10">
         <f t="shared" si="9"/>
         <v>0.14</v>
       </c>
-      <c r="AA16" s="9">
+      <c r="AA16" s="10">
         <f t="shared" si="9"/>
         <v>0.145</v>
       </c>
-      <c r="AB16" s="9">
+      <c r="AB16" s="10">
         <f t="shared" si="9"/>
         <v>0.15</v>
       </c>
-      <c r="AC16" s="9">
+      <c r="AC16" s="10">
         <f t="shared" si="9"/>
         <v>0.155</v>
       </c>
-      <c r="AD16" s="9">
+      <c r="AD16" s="10">
         <f t="shared" si="9"/>
         <v>0.16</v>
       </c>
-      <c r="AE16" s="9">
+      <c r="AE16" s="10">
         <f t="shared" si="9"/>
         <v>0.165</v>
       </c>
-      <c r="AF16" s="9">
+      <c r="AF16" s="10">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="AG16" s="9">
+      <c r="AG16" s="10">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="AH16" s="9">
+      <c r="AH16" s="10">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="AI16" s="9">
+      <c r="AI16" s="10">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="AJ16" s="9">
+      <c r="AJ16" s="10">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="AK16" s="9">
+      <c r="AK16" s="10">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="AL16" s="9">
+      <c r="AL16" s="10">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="AM16" s="9">
+      <c r="AM16" s="10">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="AN16" s="9">
+      <c r="AN16" s="10">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="AO16" s="9">
+      <c r="AO16" s="10">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="AP16" s="9">
+      <c r="AP16" s="10">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="2:42">
-      <c r="B17" s="9">
+    <row r="17" hidden="1" spans="1:42">
+      <c r="B17" s="10">
         <f>B16/B9</f>
         <v>1</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="10">
         <f t="shared" ref="C17:AP17" si="10">C16/C9</f>
         <v>1</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="Q17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="R17" s="9">
+      <c r="R17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="S17" s="9">
+      <c r="S17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="T17" s="9">
+      <c r="T17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="U17" s="9">
+      <c r="U17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="V17" s="9">
+      <c r="V17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="W17" s="9">
+      <c r="W17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="X17" s="9">
+      <c r="X17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Y17" s="9">
+      <c r="Y17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Z17" s="9">
+      <c r="Z17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AA17" s="9">
+      <c r="AA17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AB17" s="9">
+      <c r="AB17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AC17" s="9">
+      <c r="AC17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AD17" s="9">
+      <c r="AD17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AE17" s="9">
+      <c r="AE17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AF17" s="9">
+      <c r="AF17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AG17" s="9">
+      <c r="AG17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AH17" s="9">
+      <c r="AH17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AI17" s="9">
+      <c r="AI17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AJ17" s="9">
+      <c r="AJ17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AK17" s="9">
+      <c r="AK17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AL17" s="9">
+      <c r="AL17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AM17" s="9">
+      <c r="AM17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AN17" s="9">
+      <c r="AN17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AO17" s="9">
+      <c r="AO17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AP17" s="9">
+      <c r="AP17" s="10">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:2">
+    <row r="18" hidden="1" spans="1:42">
       <c r="A18" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="8">
         <f>MAX(B16:AP16)</f>
         <v>0.17</v>
       </c>
     </row>
     <row r="19" hidden="1" spans="1:42">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="9">
-        <f>B16/$B$18</f>
+      <c r="B19" s="10">
+        <f t="shared" ref="B19:AP19" si="11">B16/$B$18</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="C19" s="9">
-        <f>C16/$B$18</f>
+      <c r="C19" s="10">
+        <f t="shared" si="11"/>
         <v>0.235294117647059</v>
       </c>
-      <c r="D19" s="9">
-        <f>D16/$B$18</f>
+      <c r="D19" s="10">
+        <f t="shared" si="11"/>
         <v>0.235294117647059</v>
       </c>
-      <c r="E19" s="9">
-        <f>E16/$B$18</f>
+      <c r="E19" s="10">
+        <f t="shared" si="11"/>
         <v>0.235294117647059</v>
       </c>
-      <c r="F19" s="9">
-        <f>F16/$B$18</f>
+      <c r="F19" s="10">
+        <f t="shared" si="11"/>
         <v>0.235294117647059</v>
       </c>
-      <c r="G19" s="9">
-        <f>G16/$B$18</f>
+      <c r="G19" s="10">
+        <f t="shared" si="11"/>
         <v>0.235294117647059</v>
       </c>
-      <c r="H19" s="9">
-        <f>H16/$B$18</f>
+      <c r="H19" s="10">
+        <f t="shared" si="11"/>
         <v>0.270588235294118</v>
       </c>
-      <c r="I19" s="9">
-        <f>I16/$B$18</f>
+      <c r="I19" s="10">
+        <f t="shared" si="11"/>
         <v>0.305882352941176</v>
       </c>
-      <c r="J19" s="9">
-        <f>J16/$B$18</f>
+      <c r="J19" s="10">
+        <f t="shared" si="11"/>
         <v>0.341176470588235</v>
       </c>
-      <c r="K19" s="9">
-        <f>K16/$B$18</f>
+      <c r="K19" s="10">
+        <f t="shared" si="11"/>
         <v>0.376470588235294</v>
       </c>
-      <c r="L19" s="9">
-        <f>L16/$B$18</f>
+      <c r="L19" s="10">
+        <f t="shared" si="11"/>
         <v>0.411764705882353</v>
       </c>
-      <c r="M19" s="9">
-        <f>M16/$B$18</f>
+      <c r="M19" s="10">
+        <f t="shared" si="11"/>
         <v>0.441176470588235</v>
       </c>
-      <c r="N19" s="9">
-        <f>N16/$B$18</f>
+      <c r="N19" s="10">
+        <f t="shared" si="11"/>
         <v>0.470588235294118</v>
       </c>
-      <c r="O19" s="9">
-        <f>O16/$B$18</f>
+      <c r="O19" s="10">
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
-      <c r="P19" s="9">
-        <f>P16/$B$18</f>
+      <c r="P19" s="10">
+        <f t="shared" si="11"/>
         <v>0.529411764705882</v>
       </c>
-      <c r="Q19" s="9">
-        <f>Q16/$B$18</f>
+      <c r="Q19" s="10">
+        <f t="shared" si="11"/>
         <v>0.558823529411765</v>
       </c>
-      <c r="R19" s="9">
-        <f>R16/$B$18</f>
+      <c r="R19" s="10">
+        <f t="shared" si="11"/>
         <v>0.588235294117647</v>
       </c>
-      <c r="S19" s="9">
-        <f>S16/$B$18</f>
+      <c r="S19" s="10">
+        <f t="shared" si="11"/>
         <v>0.617647058823529</v>
       </c>
-      <c r="T19" s="9">
-        <f>T16/$B$18</f>
+      <c r="T19" s="10">
+        <f t="shared" si="11"/>
         <v>0.647058823529412</v>
       </c>
-      <c r="U19" s="9">
-        <f>U16/$B$18</f>
+      <c r="U19" s="10">
+        <f t="shared" si="11"/>
         <v>0.676470588235294</v>
       </c>
-      <c r="V19" s="9">
-        <f>V16/$B$18</f>
-        <v>0.705882352941176</v>
-      </c>
-      <c r="W19" s="9">
-        <f>W16/$B$18</f>
+      <c r="V19" s="10">
+        <f t="shared" si="11"/>
+        <v>0.705882352941177</v>
+      </c>
+      <c r="W19" s="10">
+        <f t="shared" si="11"/>
         <v>0.735294117647059</v>
       </c>
-      <c r="X19" s="9">
-        <f>X16/$B$18</f>
+      <c r="X19" s="10">
+        <f t="shared" si="11"/>
         <v>0.764705882352941</v>
       </c>
-      <c r="Y19" s="9">
-        <f>Y16/$B$18</f>
+      <c r="Y19" s="10">
+        <f t="shared" si="11"/>
         <v>0.794117647058823</v>
       </c>
-      <c r="Z19" s="9">
-        <f>Z16/$B$18</f>
+      <c r="Z19" s="10">
+        <f t="shared" si="11"/>
         <v>0.823529411764706</v>
       </c>
-      <c r="AA19" s="9">
-        <f>AA16/$B$18</f>
+      <c r="AA19" s="10">
+        <f t="shared" si="11"/>
         <v>0.852941176470588</v>
       </c>
-      <c r="AB19" s="9">
-        <f>AB16/$B$18</f>
+      <c r="AB19" s="10">
+        <f t="shared" si="11"/>
         <v>0.88235294117647</v>
       </c>
-      <c r="AC19" s="9">
-        <f>AC16/$B$18</f>
+      <c r="AC19" s="10">
+        <f t="shared" si="11"/>
         <v>0.911764705882353</v>
       </c>
-      <c r="AD19" s="9">
-        <f>AD16/$B$18</f>
+      <c r="AD19" s="10">
+        <f t="shared" si="11"/>
         <v>0.941176470588235</v>
       </c>
-      <c r="AE19" s="9">
-        <f>AE16/$B$18</f>
+      <c r="AE19" s="10">
+        <f t="shared" si="11"/>
         <v>0.970588235294118</v>
       </c>
-      <c r="AF19" s="9">
-        <f>AF16/$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="AG19" s="9">
-        <f>AG16/$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="AH19" s="9">
-        <f>AH16/$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="AI19" s="9">
-        <f>AI16/$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="AJ19" s="9">
-        <f>AJ16/$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="AK19" s="9">
-        <f>AK16/$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="AL19" s="9">
-        <f>AL16/$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="AM19" s="9">
-        <f>AM16/$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="AN19" s="9">
-        <f>AN16/$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="AO19" s="9">
-        <f>AO16/$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="AP19" s="9">
-        <f>AP16/$B$18</f>
+      <c r="AF19" s="10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AG19" s="10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AH19" s="10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AI19" s="10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AJ19" s="10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AK19" s="10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AL19" s="10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AM19" s="10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AN19" s="10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AO19" s="10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="AP19" s="10">
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -3852,163 +3847,163 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <f t="shared" ref="C22:AP22" si="11">C3*C7</f>
+        <f t="shared" ref="C22:AP22" si="12">C3*C7</f>
         <v>714.972</v>
       </c>
       <c r="D22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1547.568</v>
       </c>
       <c r="E22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2412</v>
       </c>
       <c r="F22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3480</v>
       </c>
       <c r="G22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4890</v>
       </c>
       <c r="H22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5046</v>
       </c>
       <c r="I22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5202</v>
       </c>
       <c r="J22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5358</v>
       </c>
       <c r="K22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5514</v>
       </c>
       <c r="L22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5670</v>
       </c>
       <c r="M22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5760.99999999999</v>
       </c>
       <c r="N22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5852.00000000001</v>
       </c>
       <c r="O22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5943</v>
       </c>
       <c r="P22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6033.99999999999</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6125.00000000001</v>
       </c>
       <c r="R22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6216</v>
       </c>
       <c r="S22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6306.99999999999</v>
       </c>
       <c r="T22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6398.00000000001</v>
       </c>
       <c r="U22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6489</v>
       </c>
       <c r="V22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6579.99999999999</v>
       </c>
       <c r="W22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6671.00000000001</v>
       </c>
       <c r="X22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6762</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6852.99999999999</v>
       </c>
       <c r="Z22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6944.00000000001</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7035</v>
       </c>
       <c r="AB22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7125.99999999999</v>
       </c>
       <c r="AC22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7217.00000000001</v>
       </c>
       <c r="AD22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7308</v>
       </c>
       <c r="AE22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7398.99999999999</v>
       </c>
       <c r="AF22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7490.00000000001</v>
       </c>
       <c r="AG22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7581</v>
       </c>
       <c r="AH22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7671.99999999999</v>
       </c>
       <c r="AI22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7763.00000000001</v>
       </c>
       <c r="AJ22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7854</v>
       </c>
       <c r="AK22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7944.99999999999</v>
       </c>
       <c r="AL22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8036.00000000001</v>
       </c>
       <c r="AM22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8127</v>
       </c>
       <c r="AN22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8217.99999999999</v>
       </c>
       <c r="AO22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8309.00000000001</v>
       </c>
       <c r="AP22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8400</v>
       </c>
     </row>
@@ -4021,163 +4016,163 @@
         <v>4419.08</v>
       </c>
       <c r="C23">
-        <f t="shared" ref="C23:AP23" si="12">C3*C9</f>
+        <f t="shared" ref="C23:AP23" si="13">C3*C9</f>
         <v>4766.48</v>
       </c>
       <c r="D23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5158.56</v>
       </c>
       <c r="E23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5360</v>
       </c>
       <c r="F23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5800</v>
       </c>
       <c r="G23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6520</v>
       </c>
       <c r="H23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7737.2</v>
       </c>
       <c r="I23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>9016.8</v>
       </c>
       <c r="J23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10358.8</v>
       </c>
       <c r="K23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11763.2</v>
       </c>
       <c r="L23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13230</v>
       </c>
       <c r="M23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14402.5</v>
       </c>
       <c r="N23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15605.3333333334</v>
       </c>
       <c r="O23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16838.5</v>
       </c>
       <c r="P23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>18102</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>19395.8333333334</v>
       </c>
       <c r="R23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>20720</v>
       </c>
       <c r="S23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>22074.5</v>
       </c>
       <c r="T23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>23459.3333333334</v>
       </c>
       <c r="U23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24874.5</v>
       </c>
       <c r="V23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>26320</v>
       </c>
       <c r="W23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>27795.8333333334</v>
       </c>
       <c r="X23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>29302</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>30838.5</v>
       </c>
       <c r="Z23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>32405.3333333334</v>
       </c>
       <c r="AA23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>34002.5</v>
       </c>
       <c r="AB23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>35629.9999999999</v>
       </c>
       <c r="AC23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>37287.8333333334</v>
       </c>
       <c r="AD23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>38976</v>
       </c>
       <c r="AE23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>40694.4999999999</v>
       </c>
       <c r="AF23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>42443.3333333334</v>
       </c>
       <c r="AG23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>42959</v>
       </c>
       <c r="AH23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>43474.6666666666</v>
       </c>
       <c r="AI23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>43990.3333333334</v>
       </c>
       <c r="AJ23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>44506</v>
       </c>
       <c r="AK23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>45021.6666666666</v>
       </c>
       <c r="AL23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>45537.3333333334</v>
       </c>
       <c r="AM23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>46053</v>
       </c>
       <c r="AN23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>46568.6666666666</v>
       </c>
       <c r="AO23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>47084.3333333334</v>
       </c>
       <c r="AP23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>47600</v>
       </c>
     </row>
@@ -4191,1524 +4186,1025 @@
         <v>0.235294117647059</v>
       </c>
       <c r="C25">
-        <f t="shared" ref="C25:AP25" si="13">C19</f>
+        <f t="shared" ref="C25:AP25" si="14">C19</f>
         <v>0.235294117647059</v>
       </c>
       <c r="D25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.235294117647059</v>
       </c>
       <c r="E25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.235294117647059</v>
       </c>
       <c r="F25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.235294117647059</v>
       </c>
       <c r="G25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.235294117647059</v>
       </c>
       <c r="H25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.270588235294118</v>
       </c>
       <c r="I25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.305882352941176</v>
       </c>
       <c r="J25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.341176470588235</v>
       </c>
       <c r="K25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.376470588235294</v>
       </c>
       <c r="L25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.411764705882353</v>
       </c>
       <c r="M25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.441176470588235</v>
       </c>
       <c r="N25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.470588235294118</v>
       </c>
       <c r="O25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.5</v>
       </c>
       <c r="P25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.529411764705882</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.558823529411765</v>
       </c>
       <c r="R25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.588235294117647</v>
       </c>
       <c r="S25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.617647058823529</v>
       </c>
       <c r="T25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.647058823529412</v>
       </c>
       <c r="U25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.676470588235294</v>
       </c>
       <c r="V25">
-        <f t="shared" si="13"/>
-        <v>0.705882352941176</v>
+        <f t="shared" si="14"/>
+        <v>0.705882352941177</v>
       </c>
       <c r="W25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.735294117647059</v>
       </c>
       <c r="X25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.764705882352941</v>
       </c>
       <c r="Y25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.794117647058823</v>
       </c>
       <c r="Z25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.823529411764706</v>
       </c>
       <c r="AA25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.852941176470588</v>
       </c>
       <c r="AB25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.88235294117647</v>
       </c>
       <c r="AC25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.911764705882353</v>
       </c>
       <c r="AD25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.941176470588235</v>
       </c>
       <c r="AE25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.970588235294118</v>
       </c>
       <c r="AF25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AG25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AH25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AI25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AJ25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AK25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AL25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AM25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AN25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AO25">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AP25">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" hidden="1" spans="1:2">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" hidden="1" spans="1:42">
       <c r="A26" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="27" hidden="1"/>
-    <row r="28" hidden="1" spans="2:42">
+    <row r="28" hidden="1" spans="1:42">
       <c r="B28">
         <f>$B26*B25*B23</f>
         <v>1039.78352941176</v>
       </c>
       <c r="C28">
-        <f t="shared" ref="C28:AP28" si="14">$B26*C25*C23</f>
+        <f t="shared" ref="C28:AP28" si="15">$B26*C25*C23</f>
         <v>1121.52470588235</v>
       </c>
       <c r="D28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1213.77882352941</v>
       </c>
       <c r="E28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1261.17647058824</v>
       </c>
       <c r="F28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1364.70588235294</v>
       </c>
       <c r="G28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1534.11764705882</v>
       </c>
       <c r="H28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2093.59529411765</v>
       </c>
       <c r="I28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2758.08</v>
       </c>
       <c r="J28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3534.17882352941</v>
       </c>
       <c r="K28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4428.49882352941</v>
       </c>
       <c r="L28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5447.64705882353</v>
       </c>
       <c r="M28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6354.04411764705</v>
       </c>
       <c r="N28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7343.68627450982</v>
       </c>
       <c r="O28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8419.25</v>
       </c>
       <c r="P28">
-        <f t="shared" si="14"/>
-        <v>9583.41176470586</v>
+        <f t="shared" si="15"/>
+        <v>9583.41176470587</v>
       </c>
       <c r="Q28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10838.8480392157</v>
       </c>
       <c r="R28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12188.2352941176</v>
       </c>
       <c r="S28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13634.25</v>
       </c>
       <c r="T28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15179.568627451</v>
       </c>
       <c r="U28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>16826.8676470588</v>
       </c>
       <c r="V28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>18578.8235294117</v>
       </c>
       <c r="W28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>20438.1127450981</v>
       </c>
       <c r="X28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>22407.4117647059</v>
       </c>
       <c r="Y28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>24489.3970588235</v>
       </c>
       <c r="Z28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>26686.7450980393</v>
       </c>
       <c r="AA28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>29002.1323529412</v>
       </c>
       <c r="AB28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>31438.2352941176</v>
       </c>
       <c r="AC28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>33997.7303921569</v>
       </c>
       <c r="AD28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>36683.2941176471</v>
       </c>
       <c r="AE28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>39497.6029411764</v>
       </c>
       <c r="AF28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>42443.3333333334</v>
       </c>
       <c r="AG28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>42959</v>
       </c>
       <c r="AH28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>43474.6666666666</v>
       </c>
       <c r="AI28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>43990.3333333334</v>
       </c>
       <c r="AJ28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>44506</v>
       </c>
       <c r="AK28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>45021.6666666666</v>
       </c>
       <c r="AL28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>45537.3333333334</v>
       </c>
       <c r="AM28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>46053</v>
       </c>
       <c r="AN28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>46568.6666666666</v>
       </c>
       <c r="AO28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>47084.3333333334</v>
       </c>
       <c r="AP28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>47600</v>
       </c>
     </row>
     <row r="29" hidden="1"/>
-    <row r="30" hidden="1" spans="2:42">
+    <row r="30" hidden="1" spans="1:42">
       <c r="B30">
-        <f t="shared" ref="B30:AP30" si="15">B28+B22</f>
+        <f t="shared" ref="B30:AP30" si="16">B28+B22</f>
         <v>1039.78352941176</v>
       </c>
       <c r="C30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1836.49670588235</v>
       </c>
       <c r="D30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2761.34682352941</v>
       </c>
       <c r="E30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3673.17647058824</v>
       </c>
       <c r="F30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4844.70588235294</v>
       </c>
       <c r="G30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6424.11764705882</v>
       </c>
       <c r="H30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7139.59529411765</v>
       </c>
       <c r="I30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7960.08</v>
       </c>
       <c r="J30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8892.17882352941</v>
       </c>
       <c r="K30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9942.49882352941</v>
       </c>
       <c r="L30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>11117.6470588235</v>
       </c>
       <c r="M30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>12115.044117647</v>
       </c>
       <c r="N30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>13195.6862745098</v>
       </c>
       <c r="O30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14362.25</v>
       </c>
       <c r="P30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>15617.4117647059</v>
       </c>
       <c r="Q30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>16963.8480392157</v>
       </c>
       <c r="R30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>18404.2352941176</v>
       </c>
       <c r="S30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>19941.25</v>
       </c>
       <c r="T30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>21577.568627451</v>
       </c>
       <c r="U30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>23315.8676470588</v>
       </c>
       <c r="V30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>25158.8235294117</v>
       </c>
       <c r="W30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>27109.1127450981</v>
       </c>
       <c r="X30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>29169.4117647059</v>
       </c>
       <c r="Y30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>31342.3970588235</v>
       </c>
       <c r="Z30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>33630.7450980393</v>
       </c>
       <c r="AA30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>36037.1323529412</v>
       </c>
       <c r="AB30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>38564.2352941176</v>
       </c>
       <c r="AC30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>41214.7303921569</v>
       </c>
       <c r="AD30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>43991.2941176471</v>
       </c>
       <c r="AE30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>46896.6029411764</v>
       </c>
       <c r="AF30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>49933.3333333334</v>
       </c>
       <c r="AG30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>50540</v>
       </c>
       <c r="AH30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>51146.6666666666</v>
       </c>
       <c r="AI30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>51753.3333333334</v>
       </c>
       <c r="AJ30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>52360</v>
       </c>
       <c r="AK30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>52966.6666666666</v>
       </c>
       <c r="AL30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>53573.3333333334</v>
       </c>
       <c r="AM30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>54180</v>
       </c>
       <c r="AN30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>54786.6666666666</v>
       </c>
       <c r="AO30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>55393.3333333334</v>
       </c>
       <c r="AP30">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>56000</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="2:42">
+    <row r="31" hidden="1" spans="1:42">
       <c r="B31">
-        <f t="shared" ref="B31:AP31" si="16">B30/B3</f>
+        <f t="shared" ref="B31:AP31" si="17">B30/B3</f>
         <v>0.00941176470588235</v>
       </c>
       <c r="C31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0154117647058824</v>
       </c>
       <c r="D31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0214117647058824</v>
       </c>
       <c r="E31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0274117647058824</v>
       </c>
       <c r="F31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0334117647058824</v>
       </c>
       <c r="G31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0394117647058824</v>
       </c>
       <c r="H31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0424470588235294</v>
       </c>
       <c r="I31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0459058823529412</v>
       </c>
       <c r="J31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0497882352941176</v>
       </c>
       <c r="K31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0540941176470588</v>
       </c>
       <c r="L31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0588235294117647</v>
       </c>
       <c r="M31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0630882352941177</v>
       </c>
       <c r="N31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0676470588235294</v>
       </c>
       <c r="O31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0725</v>
       </c>
       <c r="P31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0776470588235294</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0830882352941176</v>
       </c>
       <c r="R31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0888235294117647</v>
       </c>
       <c r="S31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.0948529411764706</v>
       </c>
       <c r="T31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.101176470588235</v>
       </c>
       <c r="U31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.107794117647059</v>
       </c>
       <c r="V31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.114705882352941</v>
       </c>
       <c r="W31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.121911764705882</v>
       </c>
       <c r="X31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.129411764705882</v>
       </c>
       <c r="Y31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.137205882352941</v>
       </c>
       <c r="Z31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.145294117647059</v>
       </c>
       <c r="AA31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.153676470588235</v>
       </c>
       <c r="AB31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.162352941176471</v>
       </c>
       <c r="AC31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.171323529411765</v>
       </c>
       <c r="AD31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.180588235294118</v>
       </c>
       <c r="AE31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.190147058823529</v>
       </c>
       <c r="AF31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AG31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AH31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AI31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AJ31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AK31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AL31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AM31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AN31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AO31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AP31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
     </row>
     <row r="32" hidden="1"/>
-    <row r="33" spans="1:42">
+    <row r="33" spans="1:17">
       <c r="A33" t="s">
         <v>111</v>
       </c>
-      <c r="B33" s="11">
-        <f t="shared" ref="B33:G33" si="17">B7</f>
+      <c r="B33">
+        <f t="shared" ref="B33:G33" si="18">B7</f>
         <v>0</v>
       </c>
-      <c r="C33" s="11">
-        <f t="shared" si="17"/>
+      <c r="C33">
+        <f t="shared" si="18"/>
         <v>0.006</v>
       </c>
-      <c r="D33" s="11">
-        <f t="shared" si="17"/>
+      <c r="D33">
+        <f t="shared" si="18"/>
         <v>0.012</v>
       </c>
-      <c r="E33" s="11">
-        <f t="shared" si="17"/>
+      <c r="E33">
+        <f t="shared" si="18"/>
         <v>0.018</v>
       </c>
-      <c r="F33" s="11">
-        <f t="shared" si="17"/>
+      <c r="F33">
+        <f t="shared" si="18"/>
         <v>0.024</v>
       </c>
-      <c r="G33" s="11">
-        <f t="shared" si="17"/>
+      <c r="G33">
+        <f t="shared" si="18"/>
         <v>0.03</v>
       </c>
-      <c r="H33" s="11">
-        <f>$G$33+($L$33-$G$33)*(H2-$G$2)/($L$2-$G$2)</f>
+      <c r="H33">
+        <f>G33+($L$33-$G$33)/($L$2-$G$2)</f>
         <v>0.034</v>
       </c>
-      <c r="I33" s="11">
-        <f>$G$33+($L$33-$G$33)*(I2-$G$2)/($L$2-$G$2)</f>
+      <c r="I33">
+        <f>H33+($L$33-$G$33)/($L$2-$G$2)</f>
         <v>0.038</v>
       </c>
-      <c r="J33" s="11">
-        <f>$G$33+($L$33-$G$33)*(J2-$G$2)/($L$2-$G$2)</f>
+      <c r="J33">
+        <f>I33+($L$33-$G$33)/($L$2-$G$2)</f>
         <v>0.042</v>
       </c>
-      <c r="K33" s="11">
-        <f>$G$33+($L$33-$G$33)*(K2-$G$2)/($L$2-$G$2)</f>
+      <c r="K33">
+        <f>J33+($L$33-$G$33)/($L$2-$G$2)</f>
         <v>0.046</v>
       </c>
-      <c r="L33" s="12">
+      <c r="L33">
         <v>0.05</v>
       </c>
-      <c r="M33" s="16">
-        <f>$L$33+($AA$33-$L$33)*(M2-$L$2)/($AA$2-$L$2)</f>
-        <v>0.0533333333333333</v>
-      </c>
-      <c r="N33" s="16">
-        <f t="shared" ref="N33:Z33" si="18">$L$33+($AA$33-$L$33)*(N2-$L$2)/($AA$2-$L$2)</f>
-        <v>0.0566666666666667</v>
-      </c>
-      <c r="O33" s="16">
-        <f t="shared" si="18"/>
+      <c r="M33">
+        <f>L33+($Q$33-$L$33)/($Q$2-$L$2)</f>
         <v>0.06</v>
       </c>
-      <c r="P33" s="16">
-        <f t="shared" si="18"/>
-        <v>0.0633333333333333</v>
-      </c>
-      <c r="Q33" s="16">
-        <f t="shared" si="18"/>
-        <v>0.0666666666666667</v>
-      </c>
-      <c r="R33" s="16">
-        <f t="shared" si="18"/>
+      <c r="N33">
+        <f>M33+($Q$33-$L$33)/($Q$2-$L$2)</f>
         <v>0.07</v>
       </c>
-      <c r="S33" s="16">
-        <f t="shared" si="18"/>
-        <v>0.0733333333333333</v>
-      </c>
-      <c r="T33" s="16">
-        <f t="shared" si="18"/>
-        <v>0.0766666666666667</v>
-      </c>
-      <c r="U33" s="16">
-        <f t="shared" si="18"/>
+      <c r="O33">
+        <f>N33+($Q$33-$L$33)/($Q$2-$L$2)</f>
         <v>0.08</v>
       </c>
-      <c r="V33" s="16">
-        <f t="shared" si="18"/>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="W33" s="16">
-        <f t="shared" si="18"/>
-        <v>0.0866666666666667</v>
-      </c>
-      <c r="X33" s="16">
-        <f t="shared" si="18"/>
+      <c r="P33">
+        <f>O33+($Q$33-$L$33)/($Q$2-$L$2)</f>
         <v>0.09</v>
       </c>
-      <c r="Y33" s="16">
-        <f t="shared" si="18"/>
-        <v>0.0933333333333333</v>
-      </c>
-      <c r="Z33" s="16">
-        <f t="shared" si="18"/>
-        <v>0.0966666666666667</v>
-      </c>
-      <c r="AA33" s="12">
+      <c r="Q33">
         <v>0.1</v>
       </c>
-      <c r="AB33" s="11">
-        <f>$AA$33+($AP$33-$AA$33)*(AB2-$AA$2)/($AP$2-$AA$2)</f>
-        <v>0.106666666666667</v>
-      </c>
-      <c r="AC33" s="11">
-        <f t="shared" ref="AC33:AO33" si="19">$AA$33+($AP$33-$AA$33)*(AC2-$AA$2)/($AP$2-$AA$2)</f>
-        <v>0.113333333333333</v>
-      </c>
-      <c r="AD33" s="11">
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34">
+        <f>B33*B4</f>
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <f t="shared" ref="C34:Q34" si="19">C33*C4</f>
+        <v>7149.72</v>
+      </c>
+      <c r="D34">
         <f t="shared" si="19"/>
-        <v>0.12</v>
-      </c>
-      <c r="AE33" s="11">
+        <v>15475.68</v>
+      </c>
+      <c r="E34">
         <f t="shared" si="19"/>
-        <v>0.126666666666667</v>
-      </c>
-      <c r="AF33" s="11">
+        <v>24120</v>
+      </c>
+      <c r="F34">
         <f t="shared" si="19"/>
-        <v>0.133333333333333</v>
-      </c>
-      <c r="AG33" s="11">
+        <v>34800</v>
+      </c>
+      <c r="G34">
         <f t="shared" si="19"/>
-        <v>0.14</v>
-      </c>
-      <c r="AH33" s="11">
+        <v>48900</v>
+      </c>
+      <c r="H34">
         <f t="shared" si="19"/>
-        <v>0.146666666666667</v>
-      </c>
-      <c r="AI33" s="11">
+        <v>57188</v>
+      </c>
+      <c r="I34">
         <f t="shared" si="19"/>
-        <v>0.153333333333333</v>
-      </c>
-      <c r="AJ33" s="11">
+        <v>65892</v>
+      </c>
+      <c r="J34">
         <f t="shared" si="19"/>
-        <v>0.16</v>
-      </c>
-      <c r="AK33" s="11">
+        <v>75012</v>
+      </c>
+      <c r="K34">
         <f t="shared" si="19"/>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="AL33" s="11">
+        <v>84548</v>
+      </c>
+      <c r="L34">
         <f t="shared" si="19"/>
-        <v>0.173333333333333</v>
-      </c>
-      <c r="AM33" s="11">
+        <v>94500</v>
+      </c>
+      <c r="M34">
         <f t="shared" si="19"/>
-        <v>0.18</v>
-      </c>
-      <c r="AN33" s="11">
+        <v>115220</v>
+      </c>
+      <c r="N34">
         <f t="shared" si="19"/>
-        <v>0.186666666666667</v>
-      </c>
-      <c r="AO33" s="11">
+        <v>136546.666666667</v>
+      </c>
+      <c r="O34">
         <f t="shared" si="19"/>
-        <v>0.193333333333333</v>
-      </c>
-      <c r="AP33" s="12">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:42">
-      <c r="A35" t="s">
-        <v>112</v>
-      </c>
-      <c r="B35">
-        <f>B33*B3</f>
+        <v>158480</v>
+      </c>
+      <c r="P34">
+        <f t="shared" si="19"/>
+        <v>181020</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="19"/>
+        <v>204166.666666667</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36">
+        <f>B34-'DRC-BDRC'!C2</f>
         <v>0</v>
       </c>
-      <c r="C35">
-        <f>C33*C3</f>
-        <v>714.972</v>
-      </c>
-      <c r="D35">
-        <f t="shared" ref="C35:AP35" si="20">D33*D3</f>
-        <v>1547.568</v>
-      </c>
-      <c r="E35">
-        <f t="shared" si="20"/>
-        <v>2412</v>
-      </c>
-      <c r="F35">
-        <f t="shared" si="20"/>
-        <v>3480</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="20"/>
-        <v>4890</v>
-      </c>
-      <c r="H35">
-        <f t="shared" si="20"/>
-        <v>5718.8</v>
-      </c>
-      <c r="I35">
-        <f t="shared" si="20"/>
-        <v>6589.2</v>
-      </c>
-      <c r="J35">
-        <f t="shared" si="20"/>
-        <v>7501.2</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="20"/>
-        <v>8454.8</v>
-      </c>
-      <c r="L35">
-        <f t="shared" si="20"/>
-        <v>9450</v>
-      </c>
-      <c r="M35">
-        <f t="shared" si="20"/>
-        <v>10241.7777777778</v>
-      </c>
-      <c r="N35">
-        <f t="shared" si="20"/>
-        <v>11053.7777777778</v>
-      </c>
-      <c r="O35">
-        <f t="shared" si="20"/>
-        <v>11886</v>
-      </c>
-      <c r="P35">
-        <f t="shared" si="20"/>
-        <v>12738.4444444444</v>
-      </c>
-      <c r="Q35">
-        <f t="shared" si="20"/>
-        <v>13611.1111111111</v>
-      </c>
-      <c r="R35">
-        <f t="shared" si="20"/>
-        <v>14504</v>
-      </c>
-      <c r="S35">
-        <f t="shared" si="20"/>
-        <v>15417.1111111111</v>
-      </c>
-      <c r="T35">
-        <f t="shared" si="20"/>
-        <v>16350.4444444445</v>
-      </c>
-      <c r="U35">
-        <f t="shared" si="20"/>
-        <v>17304</v>
-      </c>
-      <c r="V35">
-        <f t="shared" si="20"/>
-        <v>18277.7777777778</v>
-      </c>
-      <c r="W35">
-        <f t="shared" si="20"/>
-        <v>19271.7777777778</v>
-      </c>
-      <c r="X35">
-        <f t="shared" si="20"/>
-        <v>20286</v>
-      </c>
-      <c r="Y35">
-        <f t="shared" si="20"/>
-        <v>21320.4444444444</v>
-      </c>
-      <c r="Z35">
-        <f t="shared" si="20"/>
-        <v>22375.1111111111</v>
-      </c>
-      <c r="AA35">
-        <f t="shared" si="20"/>
-        <v>23450</v>
-      </c>
-      <c r="AB35">
-        <f t="shared" si="20"/>
-        <v>25336.8888888889</v>
-      </c>
-      <c r="AC35">
-        <f t="shared" si="20"/>
-        <v>27264.2222222223</v>
-      </c>
-      <c r="AD35">
-        <f t="shared" si="20"/>
-        <v>29232</v>
-      </c>
-      <c r="AE35">
-        <f t="shared" si="20"/>
-        <v>31240.2222222222</v>
-      </c>
-      <c r="AF35">
-        <f t="shared" si="20"/>
-        <v>33288.8888888889</v>
-      </c>
-      <c r="AG35">
-        <f t="shared" si="20"/>
-        <v>35378</v>
-      </c>
-      <c r="AH35">
-        <f t="shared" si="20"/>
-        <v>37507.5555555555</v>
-      </c>
-      <c r="AI35">
-        <f t="shared" si="20"/>
-        <v>39677.5555555556</v>
-      </c>
-      <c r="AJ35">
-        <f t="shared" si="20"/>
-        <v>41888</v>
-      </c>
-      <c r="AK35">
-        <f t="shared" si="20"/>
-        <v>44138.8888888888</v>
-      </c>
-      <c r="AL35">
-        <f t="shared" si="20"/>
-        <v>46430.2222222223</v>
-      </c>
-      <c r="AM35">
-        <f t="shared" si="20"/>
-        <v>48762</v>
-      </c>
-      <c r="AN35">
-        <f t="shared" si="20"/>
-        <v>51134.2222222222</v>
-      </c>
-      <c r="AO35">
-        <f t="shared" si="20"/>
-        <v>53546.888888889</v>
-      </c>
-      <c r="AP35">
-        <f t="shared" si="20"/>
-        <v>56000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:42">
-      <c r="A37" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" s="12">
-        <f>B33-B7</f>
+      <c r="C36">
+        <f>C34-'DRC-BDRC'!D2</f>
         <v>0</v>
       </c>
-      <c r="C37" s="12">
-        <f t="shared" ref="C37:J37" si="21">C33-C7</f>
+      <c r="D36">
+        <f>D34-'DRC-BDRC'!E2</f>
         <v>0</v>
       </c>
-      <c r="D37" s="12">
-        <f t="shared" si="21"/>
+      <c r="E36">
+        <f>E34-'DRC-BDRC'!F2</f>
         <v>0</v>
       </c>
-      <c r="E37" s="12">
-        <f t="shared" si="21"/>
+      <c r="F36">
+        <f>F34-'DRC-BDRC'!G2</f>
         <v>0</v>
       </c>
-      <c r="F37" s="12">
-        <f t="shared" si="21"/>
+      <c r="G36">
+        <f>G34-'DRC-BDRC'!H2</f>
         <v>0</v>
       </c>
-      <c r="G37" s="12">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="12">
-        <f t="shared" si="21"/>
-        <v>0.004</v>
-      </c>
-      <c r="I37" s="12">
-        <f t="shared" si="21"/>
-        <v>0.008</v>
-      </c>
-      <c r="J37" s="12">
-        <f t="shared" si="21"/>
-        <v>0.012</v>
-      </c>
-      <c r="K37" s="12">
-        <f t="shared" ref="K37:AP37" si="22">K33-K7</f>
-        <v>0.016</v>
-      </c>
-      <c r="L37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.02</v>
-      </c>
-      <c r="M37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0233333333333333</v>
-      </c>
-      <c r="N37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0266666666666667</v>
-      </c>
-      <c r="O37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.03</v>
-      </c>
-      <c r="P37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0333333333333333</v>
-      </c>
-      <c r="Q37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0366666666666667</v>
-      </c>
-      <c r="R37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.04</v>
-      </c>
-      <c r="S37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0433333333333333</v>
-      </c>
-      <c r="T37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0466666666666667</v>
-      </c>
-      <c r="U37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.05</v>
-      </c>
-      <c r="V37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0533333333333333</v>
-      </c>
-      <c r="W37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0566666666666667</v>
-      </c>
-      <c r="X37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.06</v>
-      </c>
-      <c r="Y37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0633333333333333</v>
-      </c>
-      <c r="Z37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0666666666666667</v>
-      </c>
-      <c r="AA37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.07</v>
-      </c>
-      <c r="AB37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0766666666666667</v>
-      </c>
-      <c r="AC37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="AD37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.09</v>
-      </c>
-      <c r="AE37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.0966666666666667</v>
-      </c>
-      <c r="AF37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.103333333333333</v>
-      </c>
-      <c r="AG37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.11</v>
-      </c>
-      <c r="AH37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.116666666666667</v>
-      </c>
-      <c r="AI37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.123333333333333</v>
-      </c>
-      <c r="AJ37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.13</v>
-      </c>
-      <c r="AK37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.136666666666667</v>
-      </c>
-      <c r="AL37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.143333333333333</v>
-      </c>
-      <c r="AM37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.15</v>
-      </c>
-      <c r="AN37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.156666666666667</v>
-      </c>
-      <c r="AO37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.163333333333333</v>
-      </c>
-      <c r="AP37" s="12">
-        <f t="shared" si="22"/>
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:42">
+      <c r="H36">
+        <f>H34-'DRC-BDRC'!I2</f>
+        <v>6728.00000000001</v>
+      </c>
+      <c r="I36">
+        <f>I34-'DRC-BDRC'!J2</f>
+        <v>13872</v>
+      </c>
+      <c r="J36">
+        <f>J34-'DRC-BDRC'!K2</f>
+        <v>21432</v>
+      </c>
+      <c r="K36">
+        <f>K34-'DRC-BDRC'!L2</f>
+        <v>29408</v>
+      </c>
+      <c r="L36">
+        <f>L34-'DRC-BDRC'!M2</f>
+        <v>37800</v>
+      </c>
+      <c r="M36">
+        <f>M34-'DRC-BDRC'!N2</f>
+        <v>57609.9999999999</v>
+      </c>
+      <c r="N36">
+        <f>N34-'DRC-BDRC'!O2</f>
+        <v>78026.6666666668</v>
+      </c>
+      <c r="O36">
+        <f>O34-'DRC-BDRC'!P2</f>
+        <v>99050</v>
+      </c>
+      <c r="P36">
+        <f>P34-'DRC-BDRC'!Q2</f>
+        <v>120680</v>
+      </c>
+      <c r="Q36">
+        <f>Q34-'DRC-BDRC'!R2</f>
+        <v>142916.666666667</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38" t="s">
         <v>114</v>
       </c>
       <c r="B38">
-        <f>B37/B9</f>
+        <f>B36/'DRC-PADRC'!C2</f>
         <v>0</v>
       </c>
       <c r="C38">
-        <f t="shared" ref="C38:AP38" si="23">C37/C9</f>
+        <f>C36/'DRC-PADRC'!D2</f>
         <v>0</v>
       </c>
       <c r="D38">
-        <f t="shared" si="23"/>
+        <f>D36/'DRC-PADRC'!E2</f>
         <v>0</v>
       </c>
       <c r="E38">
-        <f t="shared" si="23"/>
+        <f>E36/'DRC-PADRC'!F2</f>
         <v>0</v>
       </c>
       <c r="F38">
-        <f t="shared" si="23"/>
+        <f>F36/'DRC-PADRC'!G2</f>
         <v>0</v>
       </c>
       <c r="G38">
-        <f t="shared" si="23"/>
+        <f>G36/'DRC-PADRC'!H2</f>
         <v>0</v>
       </c>
       <c r="H38">
-        <f t="shared" si="23"/>
+        <f>H36/'DRC-PADRC'!I2</f>
         <v>0.0869565217391305</v>
       </c>
       <c r="I38">
-        <f t="shared" si="23"/>
+        <f>I36/'DRC-PADRC'!J2</f>
         <v>0.153846153846154</v>
       </c>
       <c r="J38">
-        <f t="shared" si="23"/>
+        <f>J36/'DRC-PADRC'!K2</f>
         <v>0.206896551724138</v>
       </c>
       <c r="K38">
-        <f t="shared" si="23"/>
+        <f>K36/'DRC-PADRC'!L2</f>
         <v>0.25</v>
       </c>
       <c r="L38">
-        <f t="shared" si="23"/>
+        <f>L36/'DRC-PADRC'!M2</f>
         <v>0.285714285714286</v>
       </c>
       <c r="M38">
-        <f t="shared" si="23"/>
-        <v>0.311111111111111</v>
+        <f>M36/'DRC-PADRC'!N2</f>
+        <v>0.4</v>
       </c>
       <c r="N38">
-        <f t="shared" si="23"/>
-        <v>0.333333333333333</v>
+        <f>N36/'DRC-PADRC'!O2</f>
+        <v>0.5</v>
       </c>
       <c r="O38">
-        <f t="shared" si="23"/>
-        <v>0.352941176470588</v>
+        <f>O36/'DRC-PADRC'!P2</f>
+        <v>0.588235294117647</v>
       </c>
       <c r="P38">
-        <f t="shared" si="23"/>
-        <v>0.37037037037037</v>
+        <f>P36/'DRC-PADRC'!Q2</f>
+        <v>0.666666666666667</v>
       </c>
       <c r="Q38">
-        <f t="shared" si="23"/>
-        <v>0.385964912280702</v>
-      </c>
-      <c r="R38">
-        <f t="shared" si="23"/>
-        <v>0.4</v>
-      </c>
-      <c r="S38">
-        <f t="shared" si="23"/>
-        <v>0.412698412698413</v>
-      </c>
-      <c r="T38">
-        <f t="shared" si="23"/>
-        <v>0.424242424242424</v>
-      </c>
-      <c r="U38">
-        <f t="shared" si="23"/>
-        <v>0.434782608695652</v>
-      </c>
-      <c r="V38">
-        <f t="shared" si="23"/>
-        <v>0.444444444444445</v>
-      </c>
-      <c r="W38">
-        <f t="shared" si="23"/>
-        <v>0.453333333333333</v>
-      </c>
-      <c r="X38">
-        <f t="shared" si="23"/>
-        <v>0.461538461538462</v>
-      </c>
-      <c r="Y38">
-        <f t="shared" si="23"/>
-        <v>0.469135802469136</v>
-      </c>
-      <c r="Z38">
-        <f t="shared" si="23"/>
-        <v>0.476190476190476</v>
-      </c>
-      <c r="AA38">
-        <f t="shared" si="23"/>
-        <v>0.482758620689655</v>
-      </c>
-      <c r="AB38">
-        <f t="shared" si="23"/>
-        <v>0.511111111111111</v>
-      </c>
-      <c r="AC38">
-        <f t="shared" si="23"/>
-        <v>0.537634408602151</v>
-      </c>
-      <c r="AD38">
-        <f t="shared" si="23"/>
-        <v>0.5625</v>
-      </c>
-      <c r="AE38">
-        <f t="shared" si="23"/>
-        <v>0.585858585858586</v>
-      </c>
-      <c r="AF38">
-        <f t="shared" si="23"/>
-        <v>0.607843137254902</v>
-      </c>
-      <c r="AG38">
-        <f t="shared" si="23"/>
-        <v>0.647058823529412</v>
-      </c>
-      <c r="AH38">
-        <f t="shared" si="23"/>
-        <v>0.686274509803922</v>
-      </c>
-      <c r="AI38">
-        <f t="shared" si="23"/>
-        <v>0.725490196078431</v>
-      </c>
-      <c r="AJ38">
-        <f t="shared" si="23"/>
-        <v>0.764705882352941</v>
-      </c>
-      <c r="AK38">
-        <f t="shared" si="23"/>
-        <v>0.803921568627451</v>
-      </c>
-      <c r="AL38">
-        <f t="shared" si="23"/>
-        <v>0.843137254901961</v>
-      </c>
-      <c r="AM38">
-        <f t="shared" si="23"/>
-        <v>0.882352941176471</v>
-      </c>
-      <c r="AN38">
-        <f t="shared" si="23"/>
-        <v>0.92156862745098</v>
-      </c>
-      <c r="AO38">
-        <f t="shared" si="23"/>
-        <v>0.96078431372549</v>
-      </c>
-      <c r="AP38">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <f>Q36/'DRC-PADRC'!R2</f>
+        <v>0.736842105263158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
       <c r="A40" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40">
+        <f>B38/MAX($B$38:$Q$38)</f>
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <f t="shared" ref="C40:Q40" si="20">C38/MAX($B$38:$Q$38)</f>
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="20"/>
+        <v>0.118012422360249</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="20"/>
+        <v>0.208791208791209</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="20"/>
+        <v>0.280788177339902</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="20"/>
+        <v>0.339285714285715</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="20"/>
+        <v>0.387755102040816</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="20"/>
+        <v>0.542857142857143</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="20"/>
+        <v>0.678571428571429</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="20"/>
+        <v>0.798319327731092</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="20"/>
+        <v>0.904761904761904</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="13">
-        <f>MAX(B38:AP38)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:42">
-      <c r="A41" t="s">
-        <v>107</v>
-      </c>
-      <c r="B41" s="13">
-        <f>B38/$B40</f>
-        <v>0</v>
-      </c>
-      <c r="C41" s="13">
-        <f t="shared" ref="C41:AP41" si="24">C38/$B40</f>
-        <v>0</v>
-      </c>
-      <c r="D41" s="13">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="E41" s="13">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="F41" s="13">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="G41" s="13">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.0869565217391305</v>
-      </c>
-      <c r="I41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="J41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.206896551724138</v>
-      </c>
-      <c r="K41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.25</v>
-      </c>
-      <c r="L41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.285714285714286</v>
-      </c>
-      <c r="M41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.311111111111111</v>
-      </c>
-      <c r="N41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.333333333333333</v>
-      </c>
-      <c r="O41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.352941176470588</v>
-      </c>
-      <c r="P41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.37037037037037</v>
-      </c>
-      <c r="Q41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.385964912280702</v>
-      </c>
-      <c r="R41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.4</v>
-      </c>
-      <c r="S41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.412698412698413</v>
-      </c>
-      <c r="T41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.424242424242424</v>
-      </c>
-      <c r="U41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.434782608695652</v>
-      </c>
-      <c r="V41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.444444444444445</v>
-      </c>
-      <c r="W41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.453333333333333</v>
-      </c>
-      <c r="X41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.461538461538462</v>
-      </c>
-      <c r="Y41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.469135802469136</v>
-      </c>
-      <c r="Z41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.476190476190476</v>
-      </c>
-      <c r="AA41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.482758620689655</v>
-      </c>
-      <c r="AB41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.511111111111111</v>
-      </c>
-      <c r="AC41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.537634408602151</v>
-      </c>
-      <c r="AD41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.5625</v>
-      </c>
-      <c r="AE41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.585858585858586</v>
-      </c>
-      <c r="AF41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.607843137254902</v>
-      </c>
-      <c r="AG41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.647058823529412</v>
-      </c>
-      <c r="AH41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.686274509803922</v>
-      </c>
-      <c r="AI41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.725490196078431</v>
-      </c>
-      <c r="AJ41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.764705882352941</v>
-      </c>
-      <c r="AK41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.803921568627451</v>
-      </c>
-      <c r="AL41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.843137254901961</v>
-      </c>
-      <c r="AM41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.882352941176471</v>
-      </c>
-      <c r="AN41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.92156862745098</v>
-      </c>
-      <c r="AO41" s="13">
-        <f t="shared" si="24"/>
-        <v>0.96078431372549</v>
-      </c>
-      <c r="AP41" s="13">
-        <f t="shared" si="24"/>
-        <v>1</v>
+      <c r="B42">
+        <f>MAX($B$38:$Q$38)</f>
+        <v>0.736842105263158</v>
       </c>
     </row>
   </sheetData>
@@ -5724,9 +5220,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AQ2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="19.2181818181818" customWidth="1"/>
+    <col min="1" max="1" width="19.2212389380531" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43">
@@ -6044,7 +5540,7 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AQ3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
   </cols>
@@ -6180,7 +5676,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="2" ht="42" spans="1:43">
+    <row r="2" ht="40.5" spans="1:43">
       <c r="A2" s="2" t="s">
         <v>117</v>
       </c>
@@ -6293,7 +5789,7 @@
       </c>
       <c r="AC2" s="3">
         <f>Calculations!AB4*Calculations!AB9</f>
-        <v>356299.999999999</v>
+        <v>356300</v>
       </c>
       <c r="AD2" s="3">
         <f>Calculations!AC4*Calculations!AC9</f>
@@ -6305,7 +5801,7 @@
       </c>
       <c r="AF2" s="3">
         <f>Calculations!AE4*Calculations!AE9</f>
-        <v>406944.999999999</v>
+        <v>406945</v>
       </c>
       <c r="AG2" s="3">
         <f>Calculations!AF4*Calculations!AF9</f>
@@ -6352,7 +5848,7 @@
         <v>476000</v>
       </c>
     </row>
-    <row r="3" spans="2:32">
+    <row r="3" spans="1:43">
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
